--- a/DateBase/orders/Nha Thu_2026-10-25.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-25.xlsx
@@ -1048,6 +1048,9 @@
       <c r="C71" t="str">
         <v>367_羊齿叶_lady fern_undefined_1bunch</v>
       </c>
+      <c r="F71" t="str">
+        <v>5</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
@@ -1106,7 +1109,7 @@
         <v>0.00</v>
       </c>
       <c r="G2" t="str">
-        <v>010108101055510101015105515101015151552.5109111231010105378410110508535255558153051515102515103083681061231010450</v>
+        <v>010108101055510101015105515101015151552.5109111231010105378410110508535255558153051515102515103083681061231010455</v>
       </c>
     </row>
   </sheetData>

--- a/DateBase/orders/Nha Thu_2026-10-25.xlsx
+++ b/DateBase/orders/Nha Thu_2026-10-25.xlsx
@@ -1111,6 +1111,9 @@
       <c r="G2" t="str">
         <v>010108101055510101015105515101015151552.5109111231010105378410110508535255558153051515102515103083681061231010455</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
